--- a/data/raw/Example questionnaire.xlsx
+++ b/data/raw/Example questionnaire.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\au757887\PC_documents\_git-it\opat\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\au757887\PC_documents\_git-it\PPATonline\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EEB6E1-0BBD-4CFE-B4F0-F9911D945119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBFAA7F-DEEF-48C4-A47F-9E98BC6AA015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DCB68ECE-DBFD-4EA5-81CC-7203B783D8F9}"/>
   </bookViews>
@@ -20,35 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
   <si>
     <t>title</t>
   </si>
   <si>
-    <t>crop value</t>
-  </si>
-  <si>
-    <t>costs</t>
-  </si>
-  <si>
-    <t>time/management complexity</t>
-  </si>
-  <si>
-    <t>immediate usability</t>
-  </si>
-  <si>
-    <t>environmental impact</t>
-  </si>
-  <si>
-    <t>user health and safety</t>
-  </si>
-  <si>
     <t>rating_1to5</t>
   </si>
   <si>
-    <t>pesticide_load</t>
-  </si>
-  <si>
     <t>rating is an integer of 1, 2, 3, 4, or 5 with 5 indicating highly acceptable performance, 3 neutral, and 1 unacceptable</t>
   </si>
   <si>
@@ -82,21 +61,6 @@
     <t>New approach - fairy dust</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>4.2 kg of bordeaux mixture applied per hectare, HPLI of 1.2 means a pesticide load of 5.04</t>
-  </si>
-  <si>
-    <t>5.04</t>
-  </si>
-  <si>
-    <t>5 kg of fairy dust applied per hectare, HPLI of 0.21,05 means a pesticide load of 1,05</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
@@ -104,6 +68,24 @@
   </si>
   <si>
     <t>6.25</t>
+  </si>
+  <si>
+    <t>Time/management</t>
+  </si>
+  <si>
+    <t>Crop losses</t>
+  </si>
+  <si>
+    <t>Direct costs</t>
+  </si>
+  <si>
+    <t>Third party coordination requirements</t>
+  </si>
+  <si>
+    <t>Environmental impact</t>
+  </si>
+  <si>
+    <t>User health and safety</t>
   </si>
 </sst>
 </file>
@@ -964,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23ED5A6-8E82-40C8-856E-7E2516780679}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="22.6640625" customWidth="1"/>
@@ -972,55 +954,49 @@
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -1029,91 +1005,85 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -1122,83 +1092,77 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
